--- a/data/trans_orig/P19C11_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P19C11_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por implantes / solo 2023 en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue por implantes / solo 2023 en 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13829</t>
+          <t>13726</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30426</t>
+          <t>29878</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12974</t>
+          <t>12375</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26701</t>
+          <t>25478</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30199</t>
+          <t>30087</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50851</t>
+          <t>51118</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>275004</t>
+          <t>275552</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291601</t>
+          <t>291704</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>260906</t>
+          <t>262129</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>274633</t>
+          <t>275232</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>542186</t>
+          <t>541919</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>562838</t>
+          <t>562950</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,93%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>7739</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23650</t>
+          <t>23347</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8894</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20996</t>
+          <t>21414</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19017</t>
+          <t>19463</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39976</t>
+          <t>40310</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>483334</t>
+          <t>483637</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>499772</t>
+          <t>499245</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>480552</t>
+          <t>480134</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>492654</t>
+          <t>492435</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>968556</t>
+          <t>968222</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>989515</t>
+          <t>989069</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7271</t>
+          <t>7263</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19301</t>
+          <t>19340</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9887</t>
+          <t>10281</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21981</t>
+          <t>21393</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20553</t>
+          <t>20101</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37705</t>
+          <t>36314</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>281891</t>
+          <t>281852</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>293921</t>
+          <t>293929</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>313294</t>
+          <t>313882</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>325388</t>
+          <t>324994</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>598762</t>
+          <t>600153</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>615914</t>
+          <t>616366</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16805</t>
+          <t>15637</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2424</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10937</t>
+          <t>10525</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>6904</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22149</t>
+          <t>22849</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>293315</t>
+          <t>294483</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>306313</t>
+          <t>306917</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>462528</t>
+          <t>462940</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>471041</t>
+          <t>471175</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>761436</t>
+          <t>760736</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>776006</t>
+          <t>776681</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13683</t>
+          <t>13537</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27374</t>
+          <t>27003</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17798</t>
+          <t>17436</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28988</t>
+          <t>28738</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33683</t>
+          <t>32735</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50900</t>
+          <t>50132</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>141055</t>
+          <t>141426</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>154746</t>
+          <t>154892</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>173304</t>
+          <t>173554</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>184494</t>
+          <t>184856</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>319821</t>
+          <t>320589</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>337038</t>
+          <t>337986</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,17%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>977</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6782</t>
+          <t>6281</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6836</t>
+          <t>7073</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>246950</t>
+          <t>247451</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>252736</t>
+          <t>252755</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>244293</t>
+          <t>244507</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>493246</t>
+          <t>493009</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>498856</t>
+          <t>498732</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28438</t>
+          <t>28043</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53820</t>
+          <t>52789</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19019</t>
+          <t>20304</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>63551</t>
+          <t>64732</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>51182</t>
+          <t>47425</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>106681</t>
+          <t>104131</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>545875</t>
+          <t>546906</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>571257</t>
+          <t>571652</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>764814</t>
+          <t>763633</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>809346</t>
+          <t>808061</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1321379</t>
+          <t>1323929</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1376878</t>
+          <t>1380635</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>36927</t>
+          <t>37518</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13355</t>
+          <t>13004</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27271</t>
+          <t>26924</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>25999</t>
+          <t>25716</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>56999</t>
+          <t>56207</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>871712</t>
+          <t>871121</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>900299</t>
+          <t>899001</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>676653</t>
+          <t>677000</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>690569</t>
+          <t>690920</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1555564</t>
+          <t>1556356</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1586564</t>
+          <t>1586847</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>111338</t>
+          <t>105752</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>168678</t>
+          <t>163532</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>113688</t>
+          <t>112396</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>160699</t>
+          <t>161142</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>236545</t>
+          <t>239540</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>314939</t>
+          <t>314375</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3185543</t>
+          <t>3190689</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3242883</t>
+          <t>3248469</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3418128</t>
+          <t>3417685</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3465139</t>
+          <t>3466431</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6618109</t>
+          <t>6618673</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6696503</t>
+          <t>6693508</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C11_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P19C11_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>21559</t>
+          <t>22284</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13726</t>
+          <t>15192</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29878</t>
+          <t>32569</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>18317</t>
+          <t>18675</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12375</t>
+          <t>13455</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25478</t>
+          <t>25514</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>39876</t>
+          <t>40958</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30087</t>
+          <t>31459</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51118</t>
+          <t>51998</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>283871</t>
+          <t>278633</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>275552</t>
+          <t>268348</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291704</t>
+          <t>285725</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>269290</t>
+          <t>290789</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>262129</t>
+          <t>283950</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>275232</t>
+          <t>296009</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>553161</t>
+          <t>569423</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>541919</t>
+          <t>558383</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>562950</t>
+          <t>578922</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,85%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>305430</t>
+          <t>300917</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>305430</t>
+          <t>300917</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>305430</t>
+          <t>300917</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>287607</t>
+          <t>309464</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>287607</t>
+          <t>309464</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>287607</t>
+          <t>309464</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>593037</t>
+          <t>610381</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>593037</t>
+          <t>610381</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>593037</t>
+          <t>610381</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,67 +1068,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13970</t>
+          <t>14346</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23347</t>
+          <t>23744</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>14666</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>9419</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>21981</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t>2,76%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,61%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>13897</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>9113</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>21414</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,17 +1138,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>27867</t>
+          <t>29012</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19463</t>
+          <t>19969</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40310</t>
+          <t>41132</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -1181,67 +1181,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>493014</t>
+          <t>503682</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>483637</t>
+          <t>494284</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>499245</t>
+          <t>509955</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>97,23%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,42%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,44%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>516946</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>509631</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>522193</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
           <t>97,24%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,39%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,47%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>487651</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>480134</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>492435</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,23%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,17 +1251,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>980665</t>
+          <t>1020628</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>968222</t>
+          <t>1008508</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>989069</t>
+          <t>1029671</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>506984</t>
+          <t>518028</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>506984</t>
+          <t>518028</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>506984</t>
+          <t>518028</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>501548</t>
+          <t>531612</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>501548</t>
+          <t>531612</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>501548</t>
+          <t>531612</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1008532</t>
+          <t>1049640</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1008532</t>
+          <t>1049640</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1008532</t>
+          <t>1049640</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12519</t>
+          <t>12115</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7263</t>
+          <t>7170</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19340</t>
+          <t>19344</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15212</t>
+          <t>15453</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10281</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21393</t>
+          <t>22493</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,22 +1481,22 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>27732</t>
+          <t>27568</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20101</t>
+          <t>20308</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36314</t>
+          <t>37031</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>288673</t>
+          <t>288116</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>281852</t>
+          <t>280887</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>293929</t>
+          <t>293061</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>320063</t>
+          <t>326252</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>313882</t>
+          <t>319212</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>324994</t>
+          <t>331386</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,27 +1594,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>608735</t>
+          <t>614367</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>600153</t>
+          <t>604904</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>616366</t>
+          <t>621627</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>301192</t>
+          <t>300231</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>301192</t>
+          <t>300231</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>301192</t>
+          <t>300231</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>335275</t>
+          <t>341705</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>335275</t>
+          <t>341705</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>335275</t>
+          <t>341705</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>636467</t>
+          <t>641935</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>636467</t>
+          <t>641935</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>636467</t>
+          <t>641935</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7742</t>
+          <t>8617</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3525</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15637</t>
+          <t>16606</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5722</t>
+          <t>6046</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2872</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10525</t>
+          <t>11042</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>13464</t>
+          <t>14662</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22849</t>
+          <t>24293</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>302378</t>
+          <t>362121</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>294483</t>
+          <t>354132</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>306917</t>
+          <t>367213</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>467743</t>
+          <t>413567</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>462940</t>
+          <t>408571</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>471175</t>
+          <t>416741</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>770121</t>
+          <t>775689</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>760736</t>
+          <t>766058</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>776681</t>
+          <t>781805</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>310120</t>
+          <t>370738</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>310120</t>
+          <t>370738</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>310120</t>
+          <t>370738</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>473465</t>
+          <t>419613</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>473465</t>
+          <t>419613</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>473465</t>
+          <t>419613</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>783585</t>
+          <t>790351</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>783585</t>
+          <t>790351</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>783585</t>
+          <t>790351</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>18876</t>
+          <t>21086</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13537</t>
+          <t>14615</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27003</t>
+          <t>30027</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>22976</t>
+          <t>23903</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17436</t>
+          <t>17928</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28738</t>
+          <t>29868</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>41853</t>
+          <t>44989</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32735</t>
+          <t>35887</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50132</t>
+          <t>55094</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,47%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>149553</t>
+          <t>168213</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>141426</t>
+          <t>159272</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>154892</t>
+          <t>174684</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>179316</t>
+          <t>195899</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>173554</t>
+          <t>189934</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>184856</t>
+          <t>201874</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>328868</t>
+          <t>364112</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>320589</t>
+          <t>354007</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>337986</t>
+          <t>373214</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,23%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>189299</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>189299</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>189299</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>202292</t>
+          <t>219802</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>202292</t>
+          <t>219802</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>202292</t>
+          <t>219802</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>370721</t>
+          <t>409101</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>370721</t>
+          <t>409101</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>370721</t>
+          <t>409101</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,22 +2440,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>945</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6281</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>372</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>1693</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7073</t>
+          <t>7093</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -2553,27 +2553,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>250877</t>
+          <t>246961</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>247451</t>
+          <t>243723</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>252755</t>
+          <t>248790</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2588,17 +2588,17 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>245991</t>
+          <t>251188</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>244507</t>
+          <t>249867</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>246350</t>
+          <t>251560</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>496868</t>
+          <t>498148</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>493009</t>
+          <t>494201</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>498732</t>
+          <t>499994</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>253732</t>
+          <t>249735</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>253732</t>
+          <t>249735</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>253732</t>
+          <t>249735</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>246350</t>
+          <t>251560</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>246350</t>
+          <t>251560</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>246350</t>
+          <t>251560</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>500082</t>
+          <t>501294</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>500082</t>
+          <t>501294</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>500082</t>
+          <t>501294</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>39631</t>
+          <t>47653</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28043</t>
+          <t>34978</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>64497</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>43479</t>
+          <t>51800</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20304</t>
+          <t>40264</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64732</t>
+          <t>65956</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>83110</t>
+          <t>99454</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47425</t>
+          <t>81683</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>104131</t>
+          <t>119013</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>560064</t>
+          <t>650027</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>546906</t>
+          <t>633183</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>571652</t>
+          <t>662702</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>784886</t>
+          <t>689586</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>763633</t>
+          <t>675430</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>808061</t>
+          <t>701122</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1344950</t>
+          <t>1339612</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1323929</t>
+          <t>1320053</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1380635</t>
+          <t>1357383</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>599695</t>
+          <t>697680</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>599695</t>
+          <t>697680</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>599695</t>
+          <t>697680</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>828365</t>
+          <t>741386</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>828365</t>
+          <t>741386</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>828365</t>
+          <t>741386</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1428060</t>
+          <t>1439066</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1428060</t>
+          <t>1439066</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1428060</t>
+          <t>1439066</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>23522</t>
+          <t>26386</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>17785</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37518</t>
+          <t>37758</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>18949</t>
+          <t>21228</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13004</t>
+          <t>14808</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26924</t>
+          <t>29681</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>42471</t>
+          <t>47614</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>25716</t>
+          <t>37173</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>56207</t>
+          <t>61832</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>885117</t>
+          <t>744664</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>871121</t>
+          <t>733292</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>899001</t>
+          <t>753265</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>684975</t>
+          <t>789079</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>677000</t>
+          <t>780626</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>690920</t>
+          <t>795499</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1570092</t>
+          <t>1533743</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1556356</t>
+          <t>1519525</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1586847</t>
+          <t>1544184</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>908639</t>
+          <t>771050</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>908639</t>
+          <t>771050</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>908639</t>
+          <t>771050</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>703924</t>
+          <t>810307</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>703924</t>
+          <t>810307</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>703924</t>
+          <t>810307</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1612563</t>
+          <t>1581357</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1612563</t>
+          <t>1581357</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1612563</t>
+          <t>1581357</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>140674</t>
+          <t>155262</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>105752</t>
+          <t>133792</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>163532</t>
+          <t>180390</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>138912</t>
+          <t>152143</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>112396</t>
+          <t>134476</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>161142</t>
+          <t>173205</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>279587</t>
+          <t>307405</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>239540</t>
+          <t>279706</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>314375</t>
+          <t>341573</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3213547</t>
+          <t>3242416</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3190689</t>
+          <t>3217288</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3248469</t>
+          <t>3263886</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3439915</t>
+          <t>3473305</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3417685</t>
+          <t>3452243</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3466431</t>
+          <t>3490972</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6653461</t>
+          <t>6715720</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6618673</t>
+          <t>6681552</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6693508</t>
+          <t>6743419</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
